--- a/reports/Debug-purgatory-20260106/For The Week Ending (Actual)_Budget_week_total.xlsx
+++ b/reports/Debug-purgatory-20260106/For The Week Ending (Actual)_Budget_week_total.xlsx
@@ -34,6 +34,72 @@
     <t>D6215</t>
   </si>
   <si>
+    <t>99200</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4054</t>
+  </si>
+  <si>
+    <t>D5206</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6720</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D6800</t>
+  </si>
+  <si>
+    <t>99150</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5201</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8030</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D4056</t>
+  </si>
+  <si>
+    <t>D5208</t>
+  </si>
+  <si>
+    <t>D5810</t>
+  </si>
+  <si>
     <t>D1010</t>
   </si>
   <si>
@@ -67,66 +133,6 @@
     <t>D8060</t>
   </si>
   <si>
-    <t>99150</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5201</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8030</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4054</t>
-  </si>
-  <si>
-    <t>D5206</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6720</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D6800</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D4056</t>
-  </si>
-  <si>
-    <t>D5208</t>
-  </si>
-  <si>
-    <t>D5810</t>
-  </si>
-  <si>
     <t>99100</t>
   </si>
   <si>
@@ -151,12 +157,6 @@
     <t>D8020</t>
   </si>
   <si>
-    <t>99200</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -190,6 +190,72 @@
     <t>Housekeeping</t>
   </si>
   <si>
+    <t>Winter Season Pass Visits  - Home Resort</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
+    <t>Grounds Maintenance</t>
+  </si>
+  <si>
+    <t>Mountain G&amp;A</t>
+  </si>
+  <si>
+    <t>Purg Sports Resort</t>
+  </si>
+  <si>
+    <t>Hoody's</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Guest Services</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Commercial Tenants</t>
+  </si>
+  <si>
+    <t>Comp Tickets</t>
+  </si>
+  <si>
+    <t>Vehicle Maintenance</t>
+  </si>
+  <si>
+    <t>F&amp;B Admin</t>
+  </si>
+  <si>
+    <t>Powderhouse</t>
+  </si>
+  <si>
+    <t>General Administration</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>Branded</t>
+  </si>
+  <si>
+    <t>Purgy's</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
     <t>Lift Operations</t>
   </si>
   <si>
@@ -223,66 +289,6 @@
     <t>IT Services</t>
   </si>
   <si>
-    <t>Comp Tickets</t>
-  </si>
-  <si>
-    <t>Vehicle Maintenance</t>
-  </si>
-  <si>
-    <t>F&amp;B Admin</t>
-  </si>
-  <si>
-    <t>Powderhouse</t>
-  </si>
-  <si>
-    <t>General Administration</t>
-  </si>
-  <si>
-    <t>Executive</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>Grounds Maintenance</t>
-  </si>
-  <si>
-    <t>Mountain G&amp;A</t>
-  </si>
-  <si>
-    <t>Purg Sports Resort</t>
-  </si>
-  <si>
-    <t>Hoody's</t>
-  </si>
-  <si>
-    <t>Resort Services G&amp;A</t>
-  </si>
-  <si>
-    <t>Guest Services</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Commercial Tenants</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>Branded</t>
-  </si>
-  <si>
-    <t>Purgy's</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
     <t>Daily Winter Ticketed</t>
   </si>
   <si>
@@ -305,12 +311,6 @@
   </si>
   <si>
     <t>Accounting</t>
-  </si>
-  <si>
-    <t>Winter Season Pass Visits  - Home Resort</t>
-  </si>
-  <si>
-    <t>Risk Management</t>
   </si>
 </sst>
 </file>
@@ -799,10 +799,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2">
-        <v>32142.69</v>
+        <v>10326.00</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>58</v>
@@ -816,7 +816,7 @@
         <v>48</v>
       </c>
       <c r="C10" s="2">
-        <v>5690.30</v>
+        <v>1590.47</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>59</v>
@@ -827,10 +827,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2">
-        <v>30380.38</v>
+        <v>2956.97</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>60</v>
@@ -838,16 +838,16 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="2">
-        <v>7543.03</v>
+        <v>12779.70</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -855,10 +855,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2">
-        <v>1233730.74</v>
+        <v>2485.93</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>61</v>
@@ -872,7 +872,7 @@
         <v>48</v>
       </c>
       <c r="C14" s="2">
-        <v>3830.80</v>
+        <v>3774.80</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>62</v>
@@ -886,7 +886,7 @@
         <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>19331.46</v>
+        <v>91907.63</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>62</v>
@@ -897,10 +897,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2">
-        <v>25975.73</v>
+        <v>3781.30</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>63</v>
@@ -911,10 +911,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2">
-        <v>4284.80</v>
+        <v>6758.17</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>63</v>
@@ -928,7 +928,7 @@
         <v>48</v>
       </c>
       <c r="C18" s="2">
-        <v>1227.61</v>
+        <v>3103.91</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>64</v>
@@ -942,7 +942,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>7798.20</v>
+        <v>5040.84</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>64</v>
@@ -956,7 +956,7 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>9542.91</v>
+        <v>2739.59</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>65</v>
@@ -970,7 +970,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>34044.82</v>
+        <v>8340.30</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>65</v>
@@ -984,7 +984,7 @@
         <v>48</v>
       </c>
       <c r="C22" s="2">
-        <v>8334.41</v>
+        <v>1322.80</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>66</v>
@@ -998,7 +998,7 @@
         <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>12218.15</v>
+        <v>1548.75</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>66</v>
@@ -1012,7 +1012,7 @@
         <v>48</v>
       </c>
       <c r="C24" s="2">
-        <v>7950.03</v>
+        <v>6945.50</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>67</v>
@@ -1026,7 +1026,7 @@
         <v>49</v>
       </c>
       <c r="C25" s="2">
-        <v>11450.53</v>
+        <v>6042.96</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>67</v>
@@ -1037,10 +1037,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C26" s="2">
-        <v>5634.22</v>
+        <v>0.00</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>68</v>
@@ -1163,10 +1163,10 @@
         <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2">
-        <v>2956.97</v>
+        <v>947.60</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>76</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="2">
-        <v>12779.70</v>
+        <v>32992.40</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1194,7 +1194,7 @@
         <v>48</v>
       </c>
       <c r="C37" s="2">
-        <v>2485.93</v>
+        <v>1102.50</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>77</v>
@@ -1208,7 +1208,7 @@
         <v>48</v>
       </c>
       <c r="C38" s="2">
-        <v>3774.80</v>
+        <v>20377.30</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>78</v>
@@ -1222,7 +1222,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="2">
-        <v>91907.63</v>
+        <v>101622.87</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>78</v>
@@ -1236,7 +1236,7 @@
         <v>48</v>
       </c>
       <c r="C40" s="2">
-        <v>3781.30</v>
+        <v>1408.75</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>79</v>
@@ -1250,7 +1250,7 @@
         <v>49</v>
       </c>
       <c r="C41" s="2">
-        <v>6758.17</v>
+        <v>0.00</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>79</v>
@@ -1264,7 +1264,7 @@
         <v>48</v>
       </c>
       <c r="C42" s="2">
-        <v>3103.91</v>
+        <v>32142.69</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>80</v>
@@ -1272,128 +1272,128 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="2">
-        <v>5040.84</v>
+        <v>5690.30</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="2">
-        <v>2739.59</v>
+        <v>30380.38</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2">
-        <v>8340.30</v>
+        <v>7543.03</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2">
-        <v>1322.80</v>
+        <v>1233730.74</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="2">
-        <v>1548.75</v>
+        <v>3830.80</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C48" s="2">
-        <v>6945.50</v>
+        <v>19331.46</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>6042.96</v>
+        <v>25975.73</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="2">
-        <v>0.00</v>
+        <v>4284.80</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C51" s="2">
-        <v>947.60</v>
+        <v>1227.61</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1404,7 +1404,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="2">
-        <v>32992.40</v>
+        <v>7798.20</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>86</v>
@@ -1412,16 +1412,16 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C53" s="2">
-        <v>1102.50</v>
+        <v>9542.91</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1429,10 +1429,10 @@
         <v>35</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C54" s="2">
-        <v>20377.30</v>
+        <v>34044.82</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>87</v>
@@ -1440,16 +1440,16 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C55" s="2">
-        <v>101622.87</v>
+        <v>8334.41</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1457,10 +1457,10 @@
         <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C56" s="2">
-        <v>1408.75</v>
+        <v>12218.15</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>88</v>
@@ -1468,16 +1468,16 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C57" s="2">
-        <v>0.00</v>
+        <v>7950.03</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1485,10 +1485,10 @@
         <v>37</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C58" s="2">
-        <v>6506.00</v>
+        <v>11450.53</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>89</v>
@@ -1502,7 +1502,7 @@
         <v>48</v>
       </c>
       <c r="C59" s="2">
-        <v>34935.56</v>
+        <v>5634.22</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>90</v>
@@ -1510,142 +1510,142 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C60" s="2">
-        <v>152890.98</v>
+        <v>6506.00</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C61" s="2">
-        <v>1962.54</v>
+        <v>34935.56</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="2">
-        <v>4970.97</v>
+        <v>152890.98</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C63" s="2">
-        <v>165577.70</v>
+        <v>1962.54</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C64" s="2">
-        <v>12017.30</v>
+        <v>4970.97</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C65" s="2">
-        <v>53087.17</v>
+        <v>165577.70</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C66" s="2">
-        <v>17513.87</v>
+        <v>12017.30</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C67" s="2">
-        <v>17317.81</v>
+        <v>53087.17</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C68" s="2">
-        <v>2499.65</v>
+        <v>17513.87</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C69" s="2">
-        <v>5114.06</v>
+        <v>17317.81</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1656,7 +1656,7 @@
         <v>48</v>
       </c>
       <c r="C70" s="2">
-        <v>5147.08</v>
+        <v>2499.65</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>96</v>
@@ -1667,10 +1667,10 @@
         <v>45</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C71" s="2">
-        <v>10326.00</v>
+        <v>5114.06</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>97</v>
@@ -1684,7 +1684,7 @@
         <v>48</v>
       </c>
       <c r="C72" s="2">
-        <v>1590.47</v>
+        <v>5147.08</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>98</v>
